--- a/data/students.xlsx
+++ b/data/students.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ayush\Desktop\Capstone\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A341C8E-82C9-4065-B968-E7955281B42E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE2EDB09-0B95-4390-83C5-A38BB5D64ED7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="39">
   <si>
     <t>Roll no</t>
   </si>
@@ -108,13 +108,40 @@
     <t>https://www.linkedin.com/in/ayushg24</t>
   </si>
   <si>
-    <t>NIT Bhopal</t>
-  </si>
-  <si>
-    <t>Infosys</t>
-  </si>
-  <si>
     <t>Sales, Consulting, Analytics, Operations, HR</t>
+  </si>
+  <si>
+    <t>Harsh Agarwal</t>
+  </si>
+  <si>
+    <t>harsha24@iitk.ac.in</t>
+  </si>
+  <si>
+    <t>Mechanical</t>
+  </si>
+  <si>
+    <t>BIT Sindri</t>
+  </si>
+  <si>
+    <t>Vedanta</t>
+  </si>
+  <si>
+    <t>akashgm24@iitk.ac.in</t>
+  </si>
+  <si>
+    <t>akashgm123@gmail.com</t>
+  </si>
+  <si>
+    <t>Aerospace Engineering</t>
+  </si>
+  <si>
+    <t>R V College of Engg</t>
+  </si>
+  <si>
+    <t>Akash G M</t>
+  </si>
+  <si>
+    <t>Consulting, Analytics</t>
   </si>
 </sst>
 </file>
@@ -458,7 +485,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:R3"/>
+  <dimension ref="A1:R10"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="18.33203125" customWidth="1"/>
@@ -469,7 +496,8 @@
     <col min="7" max="7" width="20.21875" customWidth="1"/>
     <col min="8" max="8" width="21.6640625" customWidth="1"/>
     <col min="9" max="9" width="15.33203125" customWidth="1"/>
-    <col min="10" max="10" width="10.6640625" customWidth="1"/>
+    <col min="10" max="10" width="13.33203125" customWidth="1"/>
+    <col min="11" max="11" width="11.21875" customWidth="1"/>
     <col min="13" max="14" width="10.5546875" customWidth="1"/>
     <col min="15" max="15" width="10.109375" customWidth="1"/>
     <col min="16" max="16" width="10" customWidth="1"/>
@@ -586,13 +614,13 @@
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="B3">
-        <v>241250012</v>
+        <v>241250019</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>17</v>
@@ -604,19 +632,19 @@
         <v>18</v>
       </c>
       <c r="G3" t="s">
+        <v>30</v>
+      </c>
+      <c r="H3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I3">
         <v>20</v>
       </c>
-      <c r="H3" t="s">
+      <c r="J3" t="s">
+        <v>32</v>
+      </c>
+      <c r="K3" t="s">
         <v>27</v>
-      </c>
-      <c r="I3">
-        <v>11</v>
-      </c>
-      <c r="J3" t="s">
-        <v>28</v>
-      </c>
-      <c r="K3" t="s">
-        <v>29</v>
       </c>
       <c r="L3">
         <v>90.2</v>
@@ -634,6 +662,368 @@
         <v>8.9499999999999993</v>
       </c>
       <c r="R3" s="4" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>37</v>
+      </c>
+      <c r="B4">
+        <v>241250005</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="E4">
+        <v>24</v>
+      </c>
+      <c r="F4" t="s">
+        <v>18</v>
+      </c>
+      <c r="G4" t="s">
+        <v>35</v>
+      </c>
+      <c r="H4" t="s">
+        <v>36</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="K4" t="s">
+        <v>38</v>
+      </c>
+      <c r="L4">
+        <v>80</v>
+      </c>
+      <c r="M4">
+        <v>80</v>
+      </c>
+      <c r="N4">
+        <v>75</v>
+      </c>
+      <c r="O4">
+        <v>2023</v>
+      </c>
+      <c r="Q4">
+        <v>8.5</v>
+      </c>
+      <c r="R4" s="4" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B5">
+        <v>241250012</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E5">
+        <v>24</v>
+      </c>
+      <c r="F5" t="s">
+        <v>18</v>
+      </c>
+      <c r="G5" t="s">
+        <v>20</v>
+      </c>
+      <c r="H5" t="s">
+        <v>21</v>
+      </c>
+      <c r="I5">
+        <v>22</v>
+      </c>
+      <c r="J5" t="s">
+        <v>22</v>
+      </c>
+      <c r="K5" t="s">
+        <v>23</v>
+      </c>
+      <c r="L5">
+        <v>83.6</v>
+      </c>
+      <c r="M5">
+        <v>83.4</v>
+      </c>
+      <c r="N5">
+        <v>83.2</v>
+      </c>
+      <c r="O5">
+        <v>2022</v>
+      </c>
+      <c r="Q5">
+        <v>8.35</v>
+      </c>
+      <c r="R5" s="4" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>28</v>
+      </c>
+      <c r="B6">
+        <v>241250019</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E6">
+        <v>24</v>
+      </c>
+      <c r="F6" t="s">
+        <v>18</v>
+      </c>
+      <c r="G6" t="s">
+        <v>30</v>
+      </c>
+      <c r="H6" t="s">
+        <v>31</v>
+      </c>
+      <c r="I6">
+        <v>20</v>
+      </c>
+      <c r="J6" t="s">
+        <v>32</v>
+      </c>
+      <c r="K6" t="s">
+        <v>27</v>
+      </c>
+      <c r="L6">
+        <v>90.2</v>
+      </c>
+      <c r="M6">
+        <v>88.9</v>
+      </c>
+      <c r="N6">
+        <v>86.5</v>
+      </c>
+      <c r="O6">
+        <v>2022</v>
+      </c>
+      <c r="Q6">
+        <v>8.9499999999999993</v>
+      </c>
+      <c r="R6" s="4" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>37</v>
+      </c>
+      <c r="B7">
+        <v>241250005</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="E7">
+        <v>24</v>
+      </c>
+      <c r="F7" t="s">
+        <v>18</v>
+      </c>
+      <c r="G7" t="s">
+        <v>35</v>
+      </c>
+      <c r="H7" t="s">
+        <v>36</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="K7" t="s">
+        <v>38</v>
+      </c>
+      <c r="L7">
+        <v>80</v>
+      </c>
+      <c r="M7">
+        <v>80</v>
+      </c>
+      <c r="N7">
+        <v>75</v>
+      </c>
+      <c r="O7">
+        <v>2023</v>
+      </c>
+      <c r="Q7">
+        <v>8.5</v>
+      </c>
+      <c r="R7" s="4" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>15</v>
+      </c>
+      <c r="B8">
+        <v>241250012</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E8">
+        <v>24</v>
+      </c>
+      <c r="F8" t="s">
+        <v>18</v>
+      </c>
+      <c r="G8" t="s">
+        <v>20</v>
+      </c>
+      <c r="H8" t="s">
+        <v>21</v>
+      </c>
+      <c r="I8">
+        <v>22</v>
+      </c>
+      <c r="J8" t="s">
+        <v>22</v>
+      </c>
+      <c r="K8" t="s">
+        <v>23</v>
+      </c>
+      <c r="L8">
+        <v>83.6</v>
+      </c>
+      <c r="M8">
+        <v>83.4</v>
+      </c>
+      <c r="N8">
+        <v>83.2</v>
+      </c>
+      <c r="O8">
+        <v>2022</v>
+      </c>
+      <c r="Q8">
+        <v>8.35</v>
+      </c>
+      <c r="R8" s="4" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>28</v>
+      </c>
+      <c r="B9">
+        <v>241250019</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E9">
+        <v>24</v>
+      </c>
+      <c r="F9" t="s">
+        <v>18</v>
+      </c>
+      <c r="G9" t="s">
+        <v>30</v>
+      </c>
+      <c r="H9" t="s">
+        <v>31</v>
+      </c>
+      <c r="I9">
+        <v>20</v>
+      </c>
+      <c r="J9" t="s">
+        <v>32</v>
+      </c>
+      <c r="K9" t="s">
+        <v>27</v>
+      </c>
+      <c r="L9">
+        <v>90.2</v>
+      </c>
+      <c r="M9">
+        <v>88.9</v>
+      </c>
+      <c r="N9">
+        <v>86.5</v>
+      </c>
+      <c r="O9">
+        <v>2022</v>
+      </c>
+      <c r="Q9">
+        <v>8.9499999999999993</v>
+      </c>
+      <c r="R9" s="4" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>37</v>
+      </c>
+      <c r="B10">
+        <v>241250005</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="E10">
+        <v>24</v>
+      </c>
+      <c r="F10" t="s">
+        <v>18</v>
+      </c>
+      <c r="G10" t="s">
+        <v>35</v>
+      </c>
+      <c r="H10" t="s">
+        <v>36</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="K10" t="s">
+        <v>38</v>
+      </c>
+      <c r="L10">
+        <v>80</v>
+      </c>
+      <c r="M10">
+        <v>80</v>
+      </c>
+      <c r="N10">
+        <v>75</v>
+      </c>
+      <c r="O10">
+        <v>2023</v>
+      </c>
+      <c r="Q10">
+        <v>8.5</v>
+      </c>
+      <c r="R10" s="4" t="s">
         <v>26</v>
       </c>
     </row>
@@ -645,8 +1035,29 @@
     <hyperlink ref="C3" r:id="rId4" xr:uid="{1F63E9AF-CDB1-4306-B341-120BC863E528}"/>
     <hyperlink ref="D3" r:id="rId5" xr:uid="{AFA5D0BC-207E-451A-8C1F-F443784980FD}"/>
     <hyperlink ref="R3" r:id="rId6" xr:uid="{8D72422C-9D1E-4B59-9576-018B2D820AE1}"/>
+    <hyperlink ref="C4" r:id="rId7" xr:uid="{2AFC4547-F291-4C2C-A2F4-4426CB421978}"/>
+    <hyperlink ref="D4" r:id="rId8" xr:uid="{7FD587A2-492A-4265-B96B-7563A3D0FBFA}"/>
+    <hyperlink ref="R4" r:id="rId9" xr:uid="{586EDBA1-E608-45A5-8C89-7047CD235988}"/>
+    <hyperlink ref="R10" r:id="rId10" xr:uid="{08A79D71-8304-488D-864A-2E4AB7EF2A01}"/>
+    <hyperlink ref="D10" r:id="rId11" xr:uid="{C431136F-8090-44E6-8130-637D27183799}"/>
+    <hyperlink ref="C10" r:id="rId12" xr:uid="{D3292812-A101-4962-B05D-4414277F6696}"/>
+    <hyperlink ref="R9" r:id="rId13" xr:uid="{473634E2-C362-4139-A486-9AFDC9661E25}"/>
+    <hyperlink ref="D9" r:id="rId14" xr:uid="{E69697EC-DD8A-4AEE-9708-BB8CA8436517}"/>
+    <hyperlink ref="C9" r:id="rId15" xr:uid="{4200971F-496E-4F53-A86C-DC71E9B5FFEE}"/>
+    <hyperlink ref="R8" r:id="rId16" xr:uid="{926A02E2-E124-4592-9170-BC9464B09B75}"/>
+    <hyperlink ref="D8" r:id="rId17" xr:uid="{F22B19F2-A1D1-403F-9D85-B73D9DC9D3DC}"/>
+    <hyperlink ref="C8" r:id="rId18" xr:uid="{7563ED81-F057-4305-9A2C-708E5409564A}"/>
+    <hyperlink ref="R7" r:id="rId19" xr:uid="{1B40E303-55D0-464A-864D-1B4DE1CACBD0}"/>
+    <hyperlink ref="D7" r:id="rId20" xr:uid="{13E99E9F-834F-4164-8300-077578772EA9}"/>
+    <hyperlink ref="C7" r:id="rId21" xr:uid="{0F640BD3-DFDB-478E-931A-C273BAFEA9C7}"/>
+    <hyperlink ref="R6" r:id="rId22" xr:uid="{F08D7600-8C39-4F22-A1F4-1C44745CAA52}"/>
+    <hyperlink ref="D6" r:id="rId23" xr:uid="{7390A164-7783-4DAE-8740-60A1C78E0556}"/>
+    <hyperlink ref="C6" r:id="rId24" xr:uid="{62BF6973-D28D-4330-8040-7F1B4E82C0F7}"/>
+    <hyperlink ref="R5" r:id="rId25" xr:uid="{79757E7F-8B1D-4245-A719-2268C5A7E859}"/>
+    <hyperlink ref="D5" r:id="rId26" xr:uid="{4D533575-E14A-45B7-B6EC-286424B21E39}"/>
+    <hyperlink ref="C5" r:id="rId27" xr:uid="{388D664C-2AD4-424D-832B-ED8551C13C2E}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId7"/>
+  <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId28"/>
 </worksheet>
 </file>